--- a/ZAL.DE.xlsx
+++ b/ZAL.DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CCDC61-3572-4300-8807-35C42A0B3FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32CFAAC-DD40-4F87-ADBD-E83C78F4AE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{98C648A9-E26D-4C03-ABFB-F82A267C3134}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{98C648A9-E26D-4C03-ABFB-F82A267C3134}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,45 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D4B27D74-EED9-482B-A4F1-5CEE32155A2C}</author>
+    <author>tc={922D9E6B-3DB0-4618-8FE9-39316F3AF760}</author>
+    <author>tc={E7E8705B-EDDF-4FF8-AF71-D79EA085E55F}</author>
+  </authors>
+  <commentList>
+    <comment ref="M40" authorId="0" shapeId="0" xr:uid="{D4B27D74-EED9-482B-A4F1-5CEE32155A2C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    About You Acq impact</t>
+      </text>
+    </comment>
+    <comment ref="N40" authorId="1" shapeId="0" xr:uid="{922D9E6B-3DB0-4618-8FE9-39316F3AF760}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    AboutYou acq impact</t>
+      </text>
+    </comment>
+    <comment ref="U40" authorId="2" shapeId="0" xr:uid="{E7E8705B-EDDF-4FF8-AF71-D79EA085E55F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    AboutYou Acq impact
+Adjsuted 7% growth</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>ZAL.DE</t>
   </si>
@@ -242,6 +279,12 @@
   <si>
     <t>Q425</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>Minority Interest</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +375,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -348,9 +391,11 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -368,6 +413,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -685,6 +736,21 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="M40" dT="2026-03-13T10:55:36.16" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{D4B27D74-EED9-482B-A4F1-5CEE32155A2C}">
+    <text>About You Acq impact</text>
+  </threadedComment>
+  <threadedComment ref="N40" dT="2026-03-13T10:55:51.13" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{922D9E6B-3DB0-4618-8FE9-39316F3AF760}">
+    <text>AboutYou acq impact</text>
+  </threadedComment>
+  <threadedComment ref="U40" dT="2026-03-13T10:56:50.44" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{E7E8705B-EDDF-4FF8-AF71-D79EA085E55F}">
+    <text>AboutYou Acq impact
+Adjsuted 7% growth</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBCB31F-2D56-46E3-B670-4DC6239CE78A}">
   <dimension ref="A1:J19"/>
@@ -707,7 +773,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>23.02</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -715,10 +781,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>260.3</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>66</v>
+        <v>260.39999999999998</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -730,7 +796,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>5992.1059999999998</v>
+        <v>6150.6480000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -741,11 +807,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <f>1319.3+117.7</f>
-        <v>1437</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>66</v>
+        <v>1877.4</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -753,11 +818,11 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <f>0+268.3+478.3+8.3</f>
-        <v>754.9</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>66</v>
+        <f>481.2+8.1+289.3</f>
+        <v>778.6</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -766,7 +831,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>5310.0059999999994</v>
+        <v>5051.848</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -803,8 +868,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055B6BCF-56F9-4A6F-A0B9-70CA233D4BF4}">
-  <dimension ref="A1:BM464"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055B6BCF-56F9-4A6F-A0B9-70CA233D4BF4}">
+  <dimension ref="A1:BM465"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -869,6 +934,9 @@
       <c r="T2" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="U2" s="14" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="3" spans="1:65" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -901,7 +969,10 @@
       <c r="M3" s="3">
         <v>4209.6000000000004</v>
       </c>
-      <c r="N3" s="3"/>
+      <c r="N3" s="3">
+        <f>+U3-SUM(K3:M3)</f>
+        <v>5346.8000000000011</v>
+      </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3">
         <v>10696</v>
@@ -918,7 +989,9 @@
       <c r="T3" s="3">
         <v>15296.2</v>
       </c>
-      <c r="U3" s="3"/>
+      <c r="U3" s="3">
+        <v>17560.2</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
@@ -995,7 +1068,9 @@
       <c r="M4" s="3">
         <v>61.4</v>
       </c>
-      <c r="N4" s="3"/>
+      <c r="N4" s="3">
+        <v>62</v>
+      </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3">
         <v>38.700000000000003</v>
@@ -1012,7 +1087,9 @@
       <c r="T4" s="3">
         <v>51.8</v>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="3">
+        <v>62</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
@@ -1089,7 +1166,9 @@
       <c r="M5" s="3">
         <v>68.5</v>
       </c>
-      <c r="N5" s="3"/>
+      <c r="N5" s="3">
+        <v>278.60000000000002</v>
+      </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3">
         <v>185.5</v>
@@ -1106,7 +1185,9 @@
       <c r="T5" s="3">
         <v>251</v>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="3">
+        <v>278.60000000000002</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
@@ -1193,17 +1274,20 @@
         <v>75.299618320610691</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" ref="L6:M6" si="1">+L3/L4</f>
+        <f t="shared" ref="L6:N6" si="1">+L3/L4</f>
         <v>76.71266540642722</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="1"/>
         <v>68.560260586319231</v>
       </c>
-      <c r="N6" s="3"/>
+      <c r="N6" s="3">
+        <f t="shared" si="1"/>
+        <v>86.238709677419379</v>
+      </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3">
-        <f t="shared" ref="P6:T6" si="2">+P3/P4</f>
+        <f t="shared" ref="P6:U6" si="2">+P3/P4</f>
         <v>276.38242894056845</v>
       </c>
       <c r="Q6" s="3">
@@ -1222,7 +1306,10 @@
         <f t="shared" si="2"/>
         <v>295.29343629343634</v>
       </c>
-      <c r="U6" s="3"/>
+      <c r="U6" s="3">
+        <f t="shared" si="2"/>
+        <v>283.22903225806454</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
@@ -1301,7 +1388,7 @@
         <v>1.151093439363817</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" ref="J7:T7" si="4">+J5/J4</f>
+        <f t="shared" ref="J7:U7" si="4">+J5/J4</f>
         <v>1.4382239382239383</v>
       </c>
       <c r="K7" s="3">
@@ -1309,14 +1396,17 @@
         <v>1.116412213740458</v>
       </c>
       <c r="L7" s="3">
-        <f t="shared" ref="L7:M7" si="5">+L5/L4</f>
+        <f t="shared" ref="L7:N7" si="5">+L5/L4</f>
         <v>1.2287334593572778</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="5"/>
         <v>1.1156351791530945</v>
       </c>
-      <c r="N7" s="3"/>
+      <c r="N7" s="3">
+        <f t="shared" si="5"/>
+        <v>4.4935483870967747</v>
+      </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3">
         <f t="shared" si="4"/>
@@ -1338,7 +1428,10 @@
         <f t="shared" si="4"/>
         <v>4.8455598455598459</v>
       </c>
-      <c r="U7" s="3"/>
+      <c r="U7" s="3">
+        <f t="shared" si="4"/>
+        <v>4.4935483870967747</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
@@ -1417,7 +1510,7 @@
         <v>59.732297063903282</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" ref="J8:T8" si="7">+J3/J5</f>
+        <f t="shared" ref="J8:U8" si="7">+J3/J5</f>
         <v>62.743624161073818</v>
       </c>
       <c r="K8" s="3">
@@ -1425,14 +1518,17 @@
         <v>67.447863247863239</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" ref="L8:M8" si="8">+L3/L5</f>
+        <f t="shared" ref="L8:N8" si="8">+L3/L5</f>
         <v>62.432307692307688</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="8"/>
         <v>61.454014598540148</v>
       </c>
-      <c r="N8" s="3"/>
+      <c r="N8" s="3">
+        <f t="shared" si="8"/>
+        <v>19.191672648959084</v>
+      </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3">
         <f t="shared" si="7"/>
@@ -1454,7 +1550,10 @@
         <f t="shared" si="7"/>
         <v>60.941035856573706</v>
       </c>
-      <c r="U8" s="3"/>
+      <c r="U8" s="3">
+        <f t="shared" si="7"/>
+        <v>63.030150753768844</v>
+      </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
@@ -1517,7 +1616,7 @@
         <v>0.70884616583055493</v>
       </c>
       <c r="F9" s="8" t="e">
-        <f t="shared" ref="F9:T9" si="10">+F13/F3</f>
+        <f t="shared" ref="F9:U9" si="10">+F13/F3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="8">
@@ -1534,21 +1633,24 @@
       </c>
       <c r="J9" s="8">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.70584460037651886</v>
       </c>
       <c r="K9" s="8">
         <f t="shared" si="10"/>
         <v>0.61319917885292852</v>
       </c>
       <c r="L9" s="8">
-        <f t="shared" ref="L9:M9" si="11">+L13/L3</f>
+        <f t="shared" ref="L9:N9" si="11">+L13/L3</f>
         <v>0.69862743648505454</v>
       </c>
       <c r="M9" s="8">
         <f t="shared" si="11"/>
         <v>0.71755036107943737</v>
       </c>
-      <c r="N9" s="8"/>
+      <c r="N9" s="8">
+        <f t="shared" si="11"/>
+        <v>0.76137128749906469</v>
+      </c>
       <c r="O9" s="3"/>
       <c r="P9" s="8">
         <f t="shared" si="10"/>
@@ -1570,7 +1672,10 @@
         <f t="shared" si="10"/>
         <v>0.69118473869327024</v>
       </c>
-      <c r="U9" s="3"/>
+      <c r="U9" s="8">
+        <f t="shared" si="10"/>
+        <v>0.70307285794011454</v>
+      </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
@@ -1706,7 +1811,10 @@
       <c r="M11" s="3">
         <v>2761.7</v>
       </c>
-      <c r="N11" s="3"/>
+      <c r="N11" s="3">
+        <f>+U11-SUM(K11:M11)</f>
+        <v>3758.4000000000005</v>
+      </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
@@ -1717,7 +1825,9 @@
       <c r="T11" s="3">
         <v>9657.7000000000007</v>
       </c>
-      <c r="U11" s="3"/>
+      <c r="U11" s="15">
+        <v>11278.7</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
@@ -1788,7 +1898,10 @@
       <c r="M12" s="3">
         <v>277.10000000000002</v>
       </c>
-      <c r="N12" s="3"/>
+      <c r="N12" s="3">
+        <f>+U12-SUM(K12:M12)</f>
+        <v>311.79999999999995</v>
+      </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1799,7 +1912,9 @@
       <c r="T12" s="3">
         <v>952.6</v>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="3">
+        <v>1091.3</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
@@ -1864,7 +1979,10 @@
       <c r="I13" s="9">
         <v>2388.5</v>
       </c>
-      <c r="J13" s="9"/>
+      <c r="J13" s="9">
+        <f>+T13-SUM(G13:I13)</f>
+        <v>3299.3999999999996</v>
+      </c>
       <c r="K13" s="9">
         <v>2419.5</v>
       </c>
@@ -1874,7 +1992,10 @@
       <c r="M13" s="9">
         <v>3020.6</v>
       </c>
-      <c r="N13" s="9"/>
+      <c r="N13" s="9">
+        <f>+U13-SUM(K13:M13)</f>
+        <v>4070.8999999999996</v>
+      </c>
       <c r="O13" s="3"/>
       <c r="P13" s="9">
         <v>7892</v>
@@ -1891,7 +2012,9 @@
       <c r="T13" s="9">
         <v>10572.5</v>
       </c>
-      <c r="U13" s="3"/>
+      <c r="U13" s="9">
+        <v>12346.1</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
@@ -1956,7 +2079,10 @@
       <c r="I14" s="3">
         <v>1416.7</v>
       </c>
-      <c r="J14" s="3"/>
+      <c r="J14" s="15">
+        <f>+T14-SUM(G14:I14)</f>
+        <v>1925.1999999999998</v>
+      </c>
       <c r="K14" s="3">
         <v>1473.3</v>
       </c>
@@ -1966,7 +2092,10 @@
       <c r="M14" s="3">
         <v>1825.4</v>
       </c>
-      <c r="N14" s="3"/>
+      <c r="N14" s="3">
+        <f>+U14-SUM(K14:M14)</f>
+        <v>2446.1000000000004</v>
+      </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3">
         <v>4587.8</v>
@@ -1983,7 +2112,9 @@
       <c r="T14" s="3">
         <v>6270.5</v>
       </c>
-      <c r="U14" s="3"/>
+      <c r="U14" s="15">
+        <v>7422.4</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
@@ -2062,8 +2193,8 @@
         <v>971.8</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" ref="J15:M15" si="13">+J13-J14</f>
-        <v>0</v>
+        <f t="shared" ref="J15:N15" si="13">+J13-J14</f>
+        <v>1374.1999999999998</v>
       </c>
       <c r="K15" s="3">
         <f t="shared" si="13"/>
@@ -2077,14 +2208,17 @@
         <f t="shared" si="13"/>
         <v>1195.1999999999998</v>
       </c>
-      <c r="N15" s="3"/>
+      <c r="N15" s="3">
+        <f t="shared" si="13"/>
+        <v>1624.7999999999993</v>
+      </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3">
         <f>+P13-P14</f>
         <v>3304.2</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" ref="Q15:T15" si="14">+Q13-Q14</f>
+        <f t="shared" ref="Q15:U15" si="14">+Q13-Q14</f>
         <v>4326.3</v>
       </c>
       <c r="R15" s="3">
@@ -2099,7 +2233,10 @@
         <f t="shared" si="14"/>
         <v>4302</v>
       </c>
-      <c r="U15" s="3"/>
+      <c r="U15" s="3">
+        <f t="shared" si="14"/>
+        <v>4923.7000000000007</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
@@ -2164,7 +2301,10 @@
       <c r="I16" s="3">
         <v>567.4</v>
       </c>
-      <c r="J16" s="3"/>
+      <c r="J16" s="15">
+        <f>+T16-SUM(G16:I16)</f>
+        <v>717</v>
+      </c>
       <c r="K16" s="3">
         <v>591.5</v>
       </c>
@@ -2174,7 +2314,10 @@
       <c r="M16" s="3">
         <v>734.9</v>
       </c>
-      <c r="N16" s="3"/>
+      <c r="N16" s="3">
+        <f>+U16-SUM(K16:M16)</f>
+        <v>888.90000000000009</v>
+      </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -2185,7 +2328,9 @@
       <c r="T16" s="3">
         <v>2418.4</v>
       </c>
-      <c r="U16" s="3"/>
+      <c r="U16" s="3">
+        <v>2842.3</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
@@ -2250,7 +2395,10 @@
       <c r="I17" s="3">
         <v>216.7</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="15">
+        <f>+T17-SUM(G17:I17)</f>
+        <v>342.10000000000014</v>
+      </c>
       <c r="K17" s="3">
         <v>209.9</v>
       </c>
@@ -2260,7 +2408,10 @@
       <c r="M17" s="3">
         <v>280.5</v>
       </c>
-      <c r="N17" s="3"/>
+      <c r="N17" s="3">
+        <f>+U17-SUM(K17:M17)</f>
+        <v>387.80000000000007</v>
+      </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
@@ -2271,7 +2422,9 @@
       <c r="T17" s="3">
         <v>979.2</v>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="3">
+        <v>1125.2</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
@@ -2336,7 +2489,10 @@
       <c r="I18" s="3">
         <v>116</v>
       </c>
-      <c r="J18" s="3"/>
+      <c r="J18" s="15">
+        <f>+T18-SUM(G18:I18)</f>
+        <v>147.69999999999993</v>
+      </c>
       <c r="K18" s="3">
         <v>125.6</v>
       </c>
@@ -2346,7 +2502,10 @@
       <c r="M18" s="3">
         <v>130.69999999999999</v>
       </c>
-      <c r="N18" s="3"/>
+      <c r="N18" s="3">
+        <f>+U18-SUM(K18:M18)</f>
+        <v>156.5</v>
+      </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -2357,7 +2516,9 @@
       <c r="T18" s="3">
         <v>513.29999999999995</v>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="3">
+        <v>541</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
@@ -2422,7 +2583,10 @@
       <c r="I19" s="3">
         <v>6.1</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="15">
+        <f>+T19-SUM(G19:I19)</f>
+        <v>7.1</v>
+      </c>
       <c r="K19" s="3">
         <v>3.7</v>
       </c>
@@ -2432,7 +2596,10 @@
       <c r="M19" s="3">
         <v>12.9</v>
       </c>
-      <c r="N19" s="3"/>
+      <c r="N19" s="3">
+        <f>+U19-SUM(K19:M19)</f>
+        <v>2.6999999999999993</v>
+      </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -2443,7 +2610,9 @@
       <c r="T19" s="3">
         <v>20.9</v>
       </c>
-      <c r="U19" s="3"/>
+      <c r="U19" s="3">
+        <v>25.7</v>
+      </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
@@ -2508,7 +2677,10 @@
       <c r="I20" s="3">
         <v>8.4</v>
       </c>
-      <c r="J20" s="3"/>
+      <c r="J20" s="15">
+        <f>+T20-SUM(G20:I20)</f>
+        <v>7.4000000000000021</v>
+      </c>
       <c r="K20" s="3">
         <v>1.4</v>
       </c>
@@ -2518,7 +2690,10 @@
       <c r="M20" s="3">
         <v>12.9</v>
       </c>
-      <c r="N20" s="3"/>
+      <c r="N20" s="3">
+        <f>+U20-SUM(K20:M20)</f>
+        <v>23.000000000000007</v>
+      </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
@@ -2529,7 +2704,9 @@
       <c r="T20" s="3">
         <v>20.100000000000001</v>
       </c>
-      <c r="U20" s="3"/>
+      <c r="U20" s="3">
+        <v>53.7</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
@@ -2608,8 +2785,8 @@
         <v>69.400000000000034</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" ref="J21:T21" si="16">+J15-SUM(J16:J18)+J19-J20</f>
-        <v>0</v>
+        <f t="shared" ref="J21:U21" si="16">+J15-SUM(J16:J18)+J19-J20</f>
+        <v>167.09999999999962</v>
       </c>
       <c r="K21" s="3">
         <f t="shared" si="16"/>
@@ -2623,7 +2800,10 @@
         <f t="shared" si="16"/>
         <v>49.099999999999909</v>
       </c>
-      <c r="N21" s="3"/>
+      <c r="N21" s="3">
+        <f t="shared" si="16"/>
+        <v>171.29999999999899</v>
+      </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3">
         <f t="shared" si="16"/>
@@ -2645,7 +2825,10 @@
         <f t="shared" si="16"/>
         <v>391.89999999999941</v>
       </c>
-      <c r="U21" s="3"/>
+      <c r="U21" s="3">
+        <f t="shared" si="16"/>
+        <v>387.20000000000073</v>
+      </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
@@ -2710,7 +2893,10 @@
       <c r="I22" s="3">
         <v>17.8</v>
       </c>
-      <c r="J22" s="3"/>
+      <c r="J22" s="15">
+        <f>+T22-SUM(G22:I22)</f>
+        <v>19.799999999999997</v>
+      </c>
       <c r="K22" s="3">
         <v>14.9</v>
       </c>
@@ -2720,7 +2906,10 @@
       <c r="M22" s="3">
         <v>5.3</v>
       </c>
-      <c r="N22" s="3"/>
+      <c r="N22" s="3">
+        <f>+U22-SUM(K22:M22)</f>
+        <v>7.7999999999999936</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -2731,7 +2920,9 @@
       <c r="T22" s="3">
         <v>75.7</v>
       </c>
-      <c r="U22" s="3"/>
+      <c r="U22" s="3">
+        <v>38.799999999999997</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
@@ -2796,7 +2987,10 @@
       <c r="I23" s="3">
         <v>24.2</v>
       </c>
-      <c r="J23" s="3"/>
+      <c r="J23" s="15">
+        <f>+T23-SUM(G23:I23)</f>
+        <v>23.100000000000009</v>
+      </c>
       <c r="K23" s="3">
         <v>18.2</v>
       </c>
@@ -2806,7 +3000,10 @@
       <c r="M23" s="3">
         <v>18</v>
       </c>
-      <c r="N23" s="3"/>
+      <c r="N23" s="3">
+        <f>+U23-SUM(K23:M23)</f>
+        <v>18.300000000000011</v>
+      </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -2817,7 +3014,9 @@
       <c r="T23" s="3">
         <v>93.4</v>
       </c>
-      <c r="U23" s="3"/>
+      <c r="U23" s="3">
+        <v>72.900000000000006</v>
+      </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
@@ -2882,7 +3081,10 @@
       <c r="I24" s="3">
         <v>-6.3</v>
       </c>
-      <c r="J24" s="3"/>
+      <c r="J24" s="15">
+        <f>+T24-SUM(G24:I24)</f>
+        <v>11.899999999999999</v>
+      </c>
       <c r="K24" s="3">
         <v>-0.1</v>
       </c>
@@ -2892,7 +3094,10 @@
       <c r="M24" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N24" s="3"/>
+      <c r="N24" s="3">
+        <f>+U24-SUM(K24:M24)</f>
+        <v>-3.5000000000000009</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -2903,7 +3108,9 @@
       <c r="T24" s="3">
         <v>-6.3</v>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="3">
+        <v>5.3</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
@@ -2982,8 +3189,8 @@
         <v>56.700000000000031</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" ref="J25:T25" si="18">+J21+J22-J23+J24</f>
-        <v>0</v>
+        <f t="shared" ref="J25:U25" si="18">+J21+J22-J23+J24</f>
+        <v>175.69999999999962</v>
       </c>
       <c r="K25" s="3">
         <f t="shared" si="18"/>
@@ -2997,7 +3204,10 @@
         <f t="shared" si="18"/>
         <v>37.499999999999908</v>
       </c>
-      <c r="N25" s="3"/>
+      <c r="N25" s="3">
+        <f t="shared" si="18"/>
+        <v>157.29999999999896</v>
+      </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3">
         <f t="shared" si="18"/>
@@ -3019,7 +3229,10 @@
         <f t="shared" si="18"/>
         <v>367.89999999999935</v>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="3">
+        <f t="shared" si="18"/>
+        <v>358.40000000000072</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
@@ -3084,7 +3297,10 @@
       <c r="I26" s="3">
         <v>12.5</v>
       </c>
-      <c r="J26" s="3"/>
+      <c r="J26" s="15">
+        <f>+T26-SUM(G26:I26)</f>
+        <v>55.500000000000007</v>
+      </c>
       <c r="K26" s="3">
         <v>8</v>
       </c>
@@ -3094,7 +3310,10 @@
       <c r="M26" s="3">
         <v>25</v>
       </c>
-      <c r="N26" s="3"/>
+      <c r="N26" s="3">
+        <f>+U26-SUM(K26:M26)</f>
+        <v>63.799999999999983</v>
+      </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
@@ -3105,7 +3324,9 @@
       <c r="T26" s="3">
         <v>116.9</v>
       </c>
-      <c r="U26" s="3"/>
+      <c r="U26" s="3">
+        <v>145.69999999999999</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
@@ -3152,67 +3373,64 @@
       <c r="BM26" s="7"/>
     </row>
     <row r="27" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="3">
-        <f t="shared" ref="C27:H27" si="19">+C25-C26</f>
+      <c r="B27" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="15">
         <v>0</v>
       </c>
-      <c r="D27" s="3">
-        <f t="shared" si="19"/>
+      <c r="D27" s="15">
         <v>0</v>
       </c>
-      <c r="E27" s="3">
-        <f t="shared" si="19"/>
-        <v>-8.1000000000000263</v>
-      </c>
-      <c r="F27" s="3">
-        <f t="shared" si="19"/>
+      <c r="E27" s="15">
         <v>0</v>
       </c>
-      <c r="G27" s="3">
-        <f t="shared" si="19"/>
-        <v>-9.0999999999997954</v>
-      </c>
-      <c r="H27" s="3">
-        <f t="shared" si="19"/>
-        <v>95.699999999999918</v>
-      </c>
-      <c r="I27" s="3">
-        <f>+I25-I26</f>
-        <v>44.200000000000031</v>
-      </c>
-      <c r="J27" s="3">
-        <f t="shared" ref="J27:M27" si="20">+J25-J26</f>
+      <c r="F27" s="15">
         <v>0</v>
       </c>
-      <c r="K27" s="3">
-        <f t="shared" si="20"/>
-        <v>10.100000000000048</v>
-      </c>
-      <c r="L27" s="3">
-        <f t="shared" si="20"/>
-        <v>96.599999999999966</v>
-      </c>
-      <c r="M27" s="3">
-        <f t="shared" si="20"/>
-        <v>12.499999999999908</v>
-      </c>
-      <c r="N27" s="3"/>
+      <c r="G27" s="15">
+        <v>0</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0</v>
+      </c>
+      <c r="J27" s="15">
+        <v>0</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0</v>
+      </c>
+      <c r="N27" s="15">
+        <v>-2.4</v>
+      </c>
       <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3">
-        <f>+S25-S26</f>
-        <v>83.100000000000165</v>
-      </c>
-      <c r="T27" s="3">
-        <f>+T25-T26</f>
-        <v>250.99999999999935</v>
-      </c>
-      <c r="U27" s="3"/>
+      <c r="P27" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="15">
+        <v>0</v>
+      </c>
+      <c r="R27" s="15">
+        <v>0</v>
+      </c>
+      <c r="S27" s="15">
+        <v>0</v>
+      </c>
+      <c r="T27" s="15">
+        <v>0</v>
+      </c>
+      <c r="U27" s="15">
+        <v>-2.4</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
@@ -3259,25 +3477,82 @@
       <c r="BM27" s="7"/>
     </row>
     <row r="28" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="B28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" ref="C28" si="19">C25-C26-C27</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" ref="D28" si="20">D25-D26-D27</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28" si="21">E25-E26-E27</f>
+        <v>-8.1000000000000263</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" ref="F28" si="22">F25-F26-F27</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" ref="G28" si="23">G25-G26-G27</f>
+        <v>-9.0999999999997954</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" ref="H28" si="24">H25-H26-H27</f>
+        <v>95.699999999999918</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" ref="I28" si="25">I25-I26-I27</f>
+        <v>44.200000000000031</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" ref="J28" si="26">J25-J26-J27</f>
+        <v>120.19999999999962</v>
+      </c>
+      <c r="K28" s="3">
+        <f t="shared" ref="K28" si="27">K25-K26-K27</f>
+        <v>10.100000000000048</v>
+      </c>
+      <c r="L28" s="3">
+        <f t="shared" ref="L28" si="28">L25-L26-L27</f>
+        <v>96.599999999999966</v>
+      </c>
+      <c r="M28" s="3">
+        <f t="shared" ref="M28:N28" si="29">M25-M26-M27</f>
+        <v>12.499999999999908</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="29"/>
+        <v>95.899999999998983</v>
+      </c>
       <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
+      <c r="P28" s="3">
+        <f t="shared" ref="P28:T28" si="30">P25-P26-P27</f>
+        <v>3304.2</v>
+      </c>
+      <c r="Q28" s="3">
+        <f t="shared" si="30"/>
+        <v>4326.3</v>
+      </c>
+      <c r="R28" s="3">
+        <f t="shared" si="30"/>
+        <v>4055.4999999999991</v>
+      </c>
+      <c r="S28" s="3">
+        <f t="shared" si="30"/>
+        <v>83.100000000000165</v>
+      </c>
+      <c r="T28" s="3">
+        <f t="shared" si="30"/>
+        <v>250.99999999999935</v>
+      </c>
+      <c r="U28" s="3">
+        <f>U25-U26-U27</f>
+        <v>215.10000000000073</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
@@ -3324,75 +3599,24 @@
       <c r="BM28" s="7"/>
     </row>
     <row r="29" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="10" t="e">
-        <f t="shared" ref="C29:J29" si="21">+C27/C30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D29" s="10" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E29" s="10" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F29" s="10" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G29" s="10" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H29" s="10">
-        <f t="shared" si="21"/>
-        <v>0.36935546121188695</v>
-      </c>
-      <c r="I29" s="10" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J29" s="10" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K29" s="10">
-        <f>+K27/K30</f>
-        <v>3.8981088382863939E-2</v>
-      </c>
-      <c r="L29" s="10">
-        <f t="shared" ref="L29:M29" si="22">+L27/L30</f>
-        <v>0.37111025739531295</v>
-      </c>
-      <c r="M29" s="10">
-        <f t="shared" si="22"/>
-        <v>4.8021513638109518E-2</v>
-      </c>
-      <c r="N29" s="10"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="10" t="e">
-        <f t="shared" ref="P29:S29" si="23">+P27/P30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q29" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R29" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S29" s="10">
-        <f t="shared" si="23"/>
-        <v>0.31998459761263059</v>
-      </c>
-      <c r="T29" s="10">
-        <f>+T27/T30</f>
-        <v>0.96873793901968086</v>
-      </c>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3441,39 +3665,81 @@
     </row>
     <row r="30" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3">
-        <v>259.10000000000002</v>
-      </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3">
-        <v>259.10000000000002</v>
-      </c>
-      <c r="L30" s="3">
-        <v>260.3</v>
-      </c>
-      <c r="M30" s="3">
-        <v>260.3</v>
-      </c>
-      <c r="N30" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="C30" s="10" t="e">
+        <f t="shared" ref="C30:J30" si="31">+C28/C31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D30" s="10" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E30" s="10" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F30" s="10" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="10" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H30" s="10">
+        <f t="shared" si="31"/>
+        <v>0.36935546121188695</v>
+      </c>
+      <c r="I30" s="10" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J30" s="10">
+        <f t="shared" si="31"/>
+        <v>0.46391354689308995</v>
+      </c>
+      <c r="K30" s="10">
+        <f>+K28/K31</f>
+        <v>3.8981088382863939E-2</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" ref="L30:N30" si="32">+L28/L31</f>
+        <v>0.37111025739531295</v>
+      </c>
+      <c r="M30" s="10">
+        <f t="shared" si="32"/>
+        <v>4.8021513638109518E-2</v>
+      </c>
+      <c r="N30" s="10">
+        <f t="shared" si="32"/>
+        <v>0.36827956989246924</v>
+      </c>
       <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3">
-        <v>259.7</v>
-      </c>
-      <c r="T30" s="3">
-        <v>259.10000000000002</v>
-      </c>
-      <c r="U30" s="3"/>
+      <c r="P30" s="10" t="e">
+        <f t="shared" ref="P30:S30" si="33">+P28/P31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q30" s="10" t="e">
+        <f t="shared" si="33"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R30" s="10" t="e">
+        <f t="shared" si="33"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S30" s="10">
+        <f t="shared" si="33"/>
+        <v>0.31998459761263059</v>
+      </c>
+      <c r="T30" s="10">
+        <f>+T28/T31</f>
+        <v>0.96873793901968086</v>
+      </c>
+      <c r="U30" s="10">
+        <f>+U28/U31</f>
+        <v>0.82603686635944984</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
@@ -3520,25 +3786,47 @@
       <c r="BM30" s="7"/>
     </row>
     <row r="31" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="3">
+        <v>259.10000000000002</v>
+      </c>
       <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
+      <c r="J31" s="3">
+        <f>+T31</f>
+        <v>259.10000000000002</v>
+      </c>
+      <c r="K31" s="3">
+        <v>259.10000000000002</v>
+      </c>
+      <c r="L31" s="3">
+        <v>260.3</v>
+      </c>
+      <c r="M31" s="3">
+        <v>260.3</v>
+      </c>
+      <c r="N31" s="3">
+        <v>260.39999999999998</v>
+      </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
+      <c r="S31" s="3">
+        <v>259.7</v>
+      </c>
+      <c r="T31" s="3">
+        <v>259.10000000000002</v>
+      </c>
+      <c r="U31" s="3">
+        <v>260.39999999999998</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
@@ -3585,62 +3873,37 @@
       <c r="BM31" s="7"/>
     </row>
     <row r="32" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11">
-        <v>15793</v>
-      </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11">
-        <v>15309</v>
-      </c>
-      <c r="H32" s="11">
-        <v>15309</v>
-      </c>
-      <c r="I32" s="11">
-        <v>15206</v>
-      </c>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11">
-        <v>15463</v>
-      </c>
-      <c r="L32" s="11">
-        <v>15571</v>
-      </c>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11">
-        <v>14194</v>
-      </c>
-      <c r="Q32" s="11">
-        <v>17043</v>
-      </c>
-      <c r="R32" s="11">
-        <v>16999</v>
-      </c>
-      <c r="S32" s="11">
-        <v>15793</v>
-      </c>
-      <c r="T32" s="11">
-        <v>15206</v>
-      </c>
-      <c r="U32" s="11"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="11"/>
-      <c r="Z32" s="11"/>
-      <c r="AA32" s="11"/>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="11"/>
-      <c r="AD32" s="11"/>
-      <c r="AE32" s="11"/>
-      <c r="AF32" s="11"/>
-      <c r="AG32" s="11"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
@@ -3675,37 +3938,64 @@
       <c r="BM32" s="7"/>
     </row>
     <row r="33" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
-      <c r="AB33" s="3"/>
-      <c r="AC33" s="3"/>
-      <c r="AD33" s="3"/>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="3"/>
-      <c r="AG33" s="3"/>
+      <c r="B33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11">
+        <v>15793</v>
+      </c>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11">
+        <v>15309</v>
+      </c>
+      <c r="H33" s="11">
+        <v>15309</v>
+      </c>
+      <c r="I33" s="11">
+        <v>15206</v>
+      </c>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11">
+        <v>15463</v>
+      </c>
+      <c r="L33" s="11">
+        <v>15571</v>
+      </c>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11">
+        <v>14194</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>17043</v>
+      </c>
+      <c r="R33" s="11">
+        <v>16999</v>
+      </c>
+      <c r="S33" s="11">
+        <v>15793</v>
+      </c>
+      <c r="T33" s="11">
+        <v>15206</v>
+      </c>
+      <c r="U33" s="11">
+        <v>16582</v>
+      </c>
+      <c r="V33" s="11"/>
+      <c r="W33" s="11"/>
+      <c r="X33" s="11"/>
+      <c r="Y33" s="11"/>
+      <c r="Z33" s="11"/>
+      <c r="AA33" s="11"/>
+      <c r="AB33" s="11"/>
+      <c r="AC33" s="11"/>
+      <c r="AD33" s="11"/>
+      <c r="AE33" s="11"/>
+      <c r="AF33" s="11"/>
+      <c r="AG33" s="11"/>
       <c r="AH33" s="3"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
@@ -3740,39 +4030,18 @@
       <c r="BM33" s="7"/>
     </row>
     <row r="34" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="8" t="e">
-        <f t="shared" ref="G34:L36" si="24">+G3/C3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H34" s="8" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="8">
-        <f t="shared" si="24"/>
-        <v>7.7649331629950469E-2</v>
-      </c>
-      <c r="J34" s="8" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="8">
-        <f t="shared" si="24"/>
-        <v>0.20130917947937266</v>
-      </c>
-      <c r="L34" s="8">
-        <f t="shared" si="24"/>
-        <v>4.9173970371519271E-2</v>
-      </c>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
@@ -3827,38 +4096,44 @@
     </row>
     <row r="35" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G35:L37" si="34">+G3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H35" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" si="24"/>
-        <v>3.9920159680637557E-3</v>
+        <f t="shared" si="34"/>
+        <v>7.7649331629950469E-2</v>
       </c>
       <c r="J35" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="24"/>
-        <v>5.8585858585858519E-2</v>
+        <f t="shared" si="34"/>
+        <v>0.20130917947937266</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" si="24"/>
-        <v>6.2248995983935851E-2</v>
-      </c>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
+        <f t="shared" si="34"/>
+        <v>4.9173970371519271E-2</v>
+      </c>
+      <c r="M35" s="8">
+        <f t="shared" ref="M35:M37" si="35">+M3/I3-1</f>
+        <v>0.21717507589995666</v>
+      </c>
+      <c r="N35" s="8">
+        <f t="shared" ref="N35:N37" si="36">+N3/J3-1</f>
+        <v>0.14384733869587563</v>
+      </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
@@ -3913,38 +4188,44 @@
     </row>
     <row r="36" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H36" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I36" s="8">
-        <f t="shared" si="24"/>
-        <v>6.2385321100917324E-2</v>
+        <f t="shared" si="34"/>
+        <v>3.9920159680637557E-3</v>
       </c>
       <c r="J36" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="24"/>
-        <v>5.9782608695652106E-2</v>
+        <f t="shared" si="34"/>
+        <v>5.8585858585858519E-2</v>
       </c>
       <c r="L36" s="8">
-        <f t="shared" si="24"/>
-        <v>2.5236593059936974E-2</v>
-      </c>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
+        <f t="shared" si="34"/>
+        <v>6.2248995983935851E-2</v>
+      </c>
+      <c r="M36" s="8">
+        <f t="shared" si="35"/>
+        <v>0.22067594433399607</v>
+      </c>
+      <c r="N36" s="8">
+        <f t="shared" si="36"/>
+        <v>0.19691119691119696</v>
+      </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
@@ -3999,38 +4280,44 @@
     </row>
     <row r="37" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="8" t="e">
-        <f t="shared" ref="G37:G39" si="25">+G11/C11-1</f>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H37" s="8" t="e">
-        <f t="shared" ref="H37:H39" si="26">+H11/D11-1</f>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I37" s="8">
-        <f t="shared" ref="I37:I39" si="27">+I11/E11-1</f>
-        <v>4.2898691226369356E-2</v>
+        <f t="shared" si="34"/>
+        <v>6.2385321100917324E-2</v>
       </c>
       <c r="J37" s="8" t="e">
-        <f t="shared" ref="J37:L39" si="28">+J11/F11-1</f>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K37" s="8" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L37" s="8" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
+      <c r="K37" s="8">
+        <f t="shared" si="34"/>
+        <v>5.9782608695652106E-2</v>
+      </c>
+      <c r="L37" s="8">
+        <f t="shared" si="34"/>
+        <v>2.5236593059936974E-2</v>
+      </c>
+      <c r="M37" s="8">
+        <f t="shared" si="35"/>
+        <v>0.18307426597582044</v>
+      </c>
+      <c r="N37" s="8">
+        <f t="shared" si="36"/>
+        <v>2.7395973154362419</v>
+      </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
@@ -4085,45 +4372,66 @@
     </row>
     <row r="38" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="8" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G38:G40" si="37">+G11/C11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H38" s="8" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="H38:H40" si="38">+H11/D11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I38" s="8">
-        <f t="shared" si="27"/>
-        <v>0.11075069508804436</v>
+        <f t="shared" ref="I38:I40" si="39">+I11/E11-1</f>
+        <v>4.2898691226369356E-2</v>
       </c>
       <c r="J38" s="8" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="J38:L40" si="40">+J11/F11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K38" s="8" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L38" s="8" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
+      <c r="M38" s="8">
+        <f t="shared" ref="M38:M40" si="41">+M11/I11-1</f>
+        <v>0.28361608180339282</v>
+      </c>
+      <c r="N38" s="8" t="e">
+        <f t="shared" ref="N38:N40" si="42">+N11/J11-1</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
+      <c r="Q38" s="8" t="e">
+        <f t="shared" ref="Q38:T38" si="43">+Q11/P11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R38" s="8" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S38" s="8" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T38" s="8">
+        <f t="shared" si="43"/>
+        <v>3.8261411769765052E-2</v>
+      </c>
+      <c r="U38" s="8">
+        <f>+U11/T11-1</f>
+        <v>0.167845346200441</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
@@ -4170,46 +4478,67 @@
       <c r="BM38" s="7"/>
     </row>
     <row r="39" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="12" t="e">
-        <f t="shared" si="25"/>
+      <c r="B39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="8" t="e">
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="12" t="e">
-        <f t="shared" si="26"/>
+      <c r="H39" s="8" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I39" s="12">
-        <f t="shared" si="27"/>
-        <v>4.9936260934546617E-2</v>
-      </c>
-      <c r="J39" s="12" t="e">
-        <f t="shared" si="28"/>
+      <c r="I39" s="8">
+        <f t="shared" si="39"/>
+        <v>0.11075069508804436</v>
+      </c>
+      <c r="J39" s="8" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K39" s="12">
-        <f>+K13/G13-1</f>
-        <v>7.9459266529847472E-2</v>
-      </c>
-      <c r="L39" s="12">
-        <f>+L13/H13-1</f>
-        <v>7.2601392251816055E-2</v>
-      </c>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
+      <c r="K39" s="8" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L39" s="8" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M39" s="8">
+        <f t="shared" si="41"/>
+        <v>0.15602836879432647</v>
+      </c>
+      <c r="N39" s="8" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
+      <c r="Q39" s="8" t="e">
+        <f t="shared" ref="Q39:T39" si="44">+Q12/P12-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R39" s="8" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S39" s="8" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T39" s="8">
+        <f t="shared" si="44"/>
+        <v>0.11493445692883908</v>
+      </c>
+      <c r="U39" s="8">
+        <f>+U12/T12-1</f>
+        <v>0.14560151165231994</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
@@ -4256,58 +4585,67 @@
       <c r="BM39" s="7"/>
     </row>
     <row r="40" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" s="8" t="e">
-        <f t="shared" ref="C40:H40" si="29">+C15/C13</f>
+      <c r="B40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="12" t="e">
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="D40" s="8" t="e">
-        <f t="shared" si="29"/>
+      <c r="H40" s="12" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E40" s="8">
-        <f t="shared" si="29"/>
-        <v>0.36691722713086289</v>
-      </c>
-      <c r="F40" s="8" t="e">
-        <f t="shared" si="29"/>
+      <c r="I40" s="12">
+        <f t="shared" si="39"/>
+        <v>4.9936260934546617E-2</v>
+      </c>
+      <c r="J40" s="12" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G40" s="8">
-        <f t="shared" si="29"/>
-        <v>0.38226108682073712</v>
-      </c>
-      <c r="H40" s="8">
-        <f t="shared" si="29"/>
-        <v>0.41585956416464886</v>
-      </c>
-      <c r="I40" s="8">
-        <f>+I15/I13</f>
-        <v>0.40686623403809918</v>
-      </c>
-      <c r="J40" s="8" t="e">
-        <f>+J15/J13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K40" s="8">
-        <f>+K15/K13</f>
-        <v>0.39107253564786115</v>
-      </c>
-      <c r="L40" s="8">
-        <f>+L15/L13</f>
-        <v>0.40827484039363693</v>
-      </c>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
+      <c r="K40" s="12">
+        <f>+K13/G13-1</f>
+        <v>7.9459266529847472E-2</v>
+      </c>
+      <c r="L40" s="12">
+        <f>+L13/H13-1</f>
+        <v>7.2601392251816055E-2</v>
+      </c>
+      <c r="M40" s="12">
+        <f t="shared" si="41"/>
+        <v>0.26464308143186099</v>
+      </c>
+      <c r="N40" s="12">
+        <f t="shared" si="42"/>
+        <v>0.23383039340486156</v>
+      </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
+      <c r="Q40" s="12">
+        <f t="shared" ref="Q40:T40" si="45">+Q13/P13-1</f>
+        <v>0.31196147997972634</v>
+      </c>
+      <c r="R40" s="12">
+        <f t="shared" si="45"/>
+        <v>-8.8854548966588176E-4</v>
+      </c>
+      <c r="S40" s="12">
+        <f t="shared" si="45"/>
+        <v>-1.949771866058303E-2</v>
+      </c>
+      <c r="T40" s="12">
+        <f t="shared" si="45"/>
+        <v>4.2334197631887616E-2</v>
+      </c>
+      <c r="U40" s="12">
+        <f>+U13/T13-1</f>
+        <v>0.16775597067864756</v>
+      </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
@@ -4355,57 +4693,78 @@
     </row>
     <row r="41" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" s="8" t="e">
-        <f t="shared" ref="C41:H41" si="30">+C21/C13</f>
+        <f t="shared" ref="C41:H41" si="46">+C15/C13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D41" s="8" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E41" s="8">
-        <f t="shared" si="30"/>
-        <v>-8.2640995208580707E-3</v>
+        <f t="shared" si="46"/>
+        <v>0.36691722713086289</v>
       </c>
       <c r="F41" s="8" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G41" s="8">
-        <f t="shared" si="30"/>
-        <v>2.6768983670929098E-4</v>
+        <f t="shared" si="46"/>
+        <v>0.38226108682073712</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" si="30"/>
-        <v>5.8565375302663411E-2</v>
+        <f t="shared" si="46"/>
+        <v>0.41585956416464886</v>
       </c>
       <c r="I41" s="8">
-        <f>+I21/I13</f>
-        <v>2.905589281976137E-2</v>
-      </c>
-      <c r="J41" s="8" t="e">
-        <f>+J21/J13</f>
-        <v>#DIV/0!</v>
+        <f>+I15/I13</f>
+        <v>0.40686623403809918</v>
+      </c>
+      <c r="J41" s="8">
+        <f>+J15/J13</f>
+        <v>0.41649996969145903</v>
       </c>
       <c r="K41" s="8">
-        <f>+K21/K13</f>
-        <v>8.8861334986567661E-3</v>
+        <f>+K15/K13</f>
+        <v>0.39107253564786115</v>
       </c>
       <c r="L41" s="8">
-        <f>+L21/L13</f>
-        <v>5.1250396811399937E-2</v>
-      </c>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
+        <f>+L15/L13</f>
+        <v>0.40827484039363693</v>
+      </c>
+      <c r="M41" s="8">
+        <f t="shared" ref="M41:N41" si="47">+M15/M13</f>
+        <v>0.39568297689200815</v>
+      </c>
+      <c r="N41" s="8">
+        <f t="shared" si="47"/>
+        <v>0.39912550050357398</v>
+      </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
+      <c r="Q41" s="8">
+        <f t="shared" ref="Q41:U41" si="48">+Q15/Q13</f>
+        <v>0.41783851651535642</v>
+      </c>
+      <c r="R41" s="8">
+        <f t="shared" si="48"/>
+        <v>0.39203271208723217</v>
+      </c>
+      <c r="S41" s="8">
+        <f t="shared" si="48"/>
+        <v>0.38749494730407869</v>
+      </c>
+      <c r="T41" s="8">
+        <f t="shared" si="48"/>
+        <v>0.40690470560416175</v>
+      </c>
+      <c r="U41" s="8">
+        <f t="shared" si="48"/>
+        <v>0.39880610071196576</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
@@ -4453,57 +4812,78 @@
     </row>
     <row r="42" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="8" t="e">
-        <f t="shared" ref="C42:H42" si="31">+C26/C25</f>
+        <f t="shared" ref="C42:H42" si="49">+C21/C13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D42" s="8" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="49"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E42" s="8">
-        <f t="shared" si="31"/>
-        <v>0.62499999999999922</v>
+        <f t="shared" si="49"/>
+        <v>-8.2640995208580707E-3</v>
       </c>
       <c r="F42" s="8" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="49"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G42" s="8">
-        <f t="shared" si="31"/>
-        <v>0.27200000000000446</v>
+        <f t="shared" si="49"/>
+        <v>2.6768983670929098E-4</v>
       </c>
       <c r="H42" s="8">
-        <f t="shared" si="31"/>
-        <v>0.35337837837837854</v>
+        <f t="shared" si="49"/>
+        <v>5.8565375302663411E-2</v>
       </c>
       <c r="I42" s="8">
-        <f>+I26/I25</f>
-        <v>0.220458553791887</v>
-      </c>
-      <c r="J42" s="8" t="e">
-        <f>+J26/J25</f>
-        <v>#DIV/0!</v>
+        <f>+I21/I13</f>
+        <v>2.905589281976137E-2</v>
+      </c>
+      <c r="J42" s="8">
+        <f>+J21/J13</f>
+        <v>5.0645571922167558E-2</v>
       </c>
       <c r="K42" s="8">
-        <f>+K26/K25</f>
-        <v>0.44198895027624191</v>
+        <f>+K21/K13</f>
+        <v>8.8861334986567661E-3</v>
       </c>
       <c r="L42" s="8">
-        <f>+L26/L25</f>
-        <v>0.33608247422680421</v>
-      </c>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
+        <f>+L21/L13</f>
+        <v>5.1250396811399937E-2</v>
+      </c>
+      <c r="M42" s="8">
+        <f t="shared" ref="M42:N42" si="50">+M21/M13</f>
+        <v>1.6255048665827953E-2</v>
+      </c>
+      <c r="N42" s="8">
+        <f t="shared" si="50"/>
+        <v>4.2079147117344812E-2</v>
+      </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
+      <c r="Q42" s="8">
+        <f t="shared" ref="Q42:U42" si="51">+Q21/Q13</f>
+        <v>0.41783851651535642</v>
+      </c>
+      <c r="R42" s="8">
+        <f t="shared" si="51"/>
+        <v>0.39203271208723217</v>
+      </c>
+      <c r="S42" s="8">
+        <f t="shared" si="51"/>
+        <v>1.8820676124656186E-2</v>
+      </c>
+      <c r="T42" s="8">
+        <f t="shared" si="51"/>
+        <v>3.7067864743438109E-2</v>
+      </c>
+      <c r="U42" s="8">
+        <f t="shared" si="51"/>
+        <v>3.1362130551348254E-2</v>
+      </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4550,25 +4930,79 @@
       <c r="BM42" s="7"/>
     </row>
     <row r="43" spans="2:65" x14ac:dyDescent="0.2">
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
+      <c r="B43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="8" t="e">
+        <f t="shared" ref="C43:H43" si="52">+C26/C25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D43" s="8" t="e">
+        <f t="shared" si="52"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E43" s="8">
+        <f t="shared" si="52"/>
+        <v>0.62499999999999922</v>
+      </c>
+      <c r="F43" s="8" t="e">
+        <f t="shared" si="52"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G43" s="8">
+        <f t="shared" si="52"/>
+        <v>0.27200000000000446</v>
+      </c>
+      <c r="H43" s="8">
+        <f t="shared" si="52"/>
+        <v>0.35337837837837854</v>
+      </c>
+      <c r="I43" s="8">
+        <f>+I26/I25</f>
+        <v>0.220458553791887</v>
+      </c>
+      <c r="J43" s="8">
+        <f>+J26/J25</f>
+        <v>0.31587933978372296</v>
+      </c>
+      <c r="K43" s="8">
+        <f>+K26/K25</f>
+        <v>0.44198895027624191</v>
+      </c>
+      <c r="L43" s="8">
+        <f>+L26/L25</f>
+        <v>0.33608247422680421</v>
+      </c>
+      <c r="M43" s="8">
+        <f t="shared" ref="M43:N43" si="53">+M26/M25</f>
+        <v>0.66666666666666829</v>
+      </c>
+      <c r="N43" s="8">
+        <f t="shared" si="53"/>
+        <v>0.40559440559440818</v>
+      </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
+      <c r="Q43" s="8">
+        <f t="shared" ref="Q43:U43" si="54">+Q26/Q25</f>
+        <v>0</v>
+      </c>
+      <c r="R43" s="8">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="8">
+        <f t="shared" si="54"/>
+        <v>0.45686274509803876</v>
+      </c>
+      <c r="T43" s="8">
+        <f t="shared" si="54"/>
+        <v>0.31774938842076711</v>
+      </c>
+      <c r="U43" s="8">
+        <f t="shared" si="54"/>
+        <v>0.40652901785714202</v>
+      </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
@@ -28860,49 +29294,49 @@
       <c r="BM416" s="7"/>
     </row>
     <row r="417" spans="3:65" x14ac:dyDescent="0.2">
-      <c r="C417" s="7"/>
-      <c r="D417" s="7"/>
-      <c r="E417" s="7"/>
-      <c r="F417" s="7"/>
-      <c r="G417" s="7"/>
-      <c r="H417" s="7"/>
-      <c r="I417" s="7"/>
-      <c r="J417" s="7"/>
-      <c r="K417" s="7"/>
-      <c r="L417" s="7"/>
-      <c r="M417" s="7"/>
-      <c r="N417" s="7"/>
-      <c r="O417" s="7"/>
-      <c r="P417" s="7"/>
-      <c r="Q417" s="7"/>
-      <c r="R417" s="7"/>
-      <c r="S417" s="7"/>
-      <c r="T417" s="7"/>
-      <c r="U417" s="7"/>
-      <c r="V417" s="7"/>
-      <c r="W417" s="7"/>
-      <c r="X417" s="7"/>
-      <c r="Y417" s="7"/>
-      <c r="Z417" s="7"/>
-      <c r="AA417" s="7"/>
-      <c r="AB417" s="7"/>
-      <c r="AC417" s="7"/>
-      <c r="AD417" s="7"/>
-      <c r="AE417" s="7"/>
-      <c r="AF417" s="7"/>
-      <c r="AG417" s="7"/>
-      <c r="AH417" s="7"/>
-      <c r="AI417" s="7"/>
-      <c r="AJ417" s="7"/>
-      <c r="AK417" s="7"/>
-      <c r="AL417" s="7"/>
-      <c r="AM417" s="7"/>
-      <c r="AN417" s="7"/>
-      <c r="AO417" s="7"/>
-      <c r="AP417" s="7"/>
-      <c r="AQ417" s="7"/>
-      <c r="AR417" s="7"/>
-      <c r="AS417" s="7"/>
+      <c r="C417" s="3"/>
+      <c r="D417" s="3"/>
+      <c r="E417" s="3"/>
+      <c r="F417" s="3"/>
+      <c r="G417" s="3"/>
+      <c r="H417" s="3"/>
+      <c r="I417" s="3"/>
+      <c r="J417" s="3"/>
+      <c r="K417" s="3"/>
+      <c r="L417" s="3"/>
+      <c r="M417" s="3"/>
+      <c r="N417" s="3"/>
+      <c r="O417" s="3"/>
+      <c r="P417" s="3"/>
+      <c r="Q417" s="3"/>
+      <c r="R417" s="3"/>
+      <c r="S417" s="3"/>
+      <c r="T417" s="3"/>
+      <c r="U417" s="3"/>
+      <c r="V417" s="3"/>
+      <c r="W417" s="3"/>
+      <c r="X417" s="3"/>
+      <c r="Y417" s="3"/>
+      <c r="Z417" s="3"/>
+      <c r="AA417" s="3"/>
+      <c r="AB417" s="3"/>
+      <c r="AC417" s="3"/>
+      <c r="AD417" s="3"/>
+      <c r="AE417" s="3"/>
+      <c r="AF417" s="3"/>
+      <c r="AG417" s="3"/>
+      <c r="AH417" s="3"/>
+      <c r="AI417" s="3"/>
+      <c r="AJ417" s="3"/>
+      <c r="AK417" s="3"/>
+      <c r="AL417" s="3"/>
+      <c r="AM417" s="3"/>
+      <c r="AN417" s="3"/>
+      <c r="AO417" s="3"/>
+      <c r="AP417" s="3"/>
+      <c r="AQ417" s="3"/>
+      <c r="AR417" s="3"/>
+      <c r="AS417" s="3"/>
       <c r="AT417" s="7"/>
       <c r="AU417" s="7"/>
       <c r="AV417" s="7"/>
@@ -31979,10 +32413,76 @@
       <c r="BL464" s="7"/>
       <c r="BM464" s="7"/>
     </row>
+    <row r="465" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="C465" s="7"/>
+      <c r="D465" s="7"/>
+      <c r="E465" s="7"/>
+      <c r="F465" s="7"/>
+      <c r="G465" s="7"/>
+      <c r="H465" s="7"/>
+      <c r="I465" s="7"/>
+      <c r="J465" s="7"/>
+      <c r="K465" s="7"/>
+      <c r="L465" s="7"/>
+      <c r="M465" s="7"/>
+      <c r="N465" s="7"/>
+      <c r="O465" s="7"/>
+      <c r="P465" s="7"/>
+      <c r="Q465" s="7"/>
+      <c r="R465" s="7"/>
+      <c r="S465" s="7"/>
+      <c r="T465" s="7"/>
+      <c r="U465" s="7"/>
+      <c r="V465" s="7"/>
+      <c r="W465" s="7"/>
+      <c r="X465" s="7"/>
+      <c r="Y465" s="7"/>
+      <c r="Z465" s="7"/>
+      <c r="AA465" s="7"/>
+      <c r="AB465" s="7"/>
+      <c r="AC465" s="7"/>
+      <c r="AD465" s="7"/>
+      <c r="AE465" s="7"/>
+      <c r="AF465" s="7"/>
+      <c r="AG465" s="7"/>
+      <c r="AH465" s="7"/>
+      <c r="AI465" s="7"/>
+      <c r="AJ465" s="7"/>
+      <c r="AK465" s="7"/>
+      <c r="AL465" s="7"/>
+      <c r="AM465" s="7"/>
+      <c r="AN465" s="7"/>
+      <c r="AO465" s="7"/>
+      <c r="AP465" s="7"/>
+      <c r="AQ465" s="7"/>
+      <c r="AR465" s="7"/>
+      <c r="AS465" s="7"/>
+      <c r="AT465" s="7"/>
+      <c r="AU465" s="7"/>
+      <c r="AV465" s="7"/>
+      <c r="AW465" s="7"/>
+      <c r="AX465" s="7"/>
+      <c r="AY465" s="7"/>
+      <c r="AZ465" s="7"/>
+      <c r="BA465" s="7"/>
+      <c r="BB465" s="7"/>
+      <c r="BC465" s="7"/>
+      <c r="BD465" s="7"/>
+      <c r="BE465" s="7"/>
+      <c r="BF465" s="7"/>
+      <c r="BG465" s="7"/>
+      <c r="BH465" s="7"/>
+      <c r="BI465" s="7"/>
+      <c r="BJ465" s="7"/>
+      <c r="BK465" s="7"/>
+      <c r="BL465" s="7"/>
+      <c r="BM465" s="7"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{9425B058-B76C-415F-AAD0-8E385B493264}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ZAL.DE.xlsx
+++ b/ZAL.DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BF1852-4391-4A2E-A217-C0C39665BF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E75047-B71A-4CCF-9C5E-4093906AD63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{98C648A9-E26D-4C03-ABFB-F82A267C3134}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{98C648A9-E26D-4C03-ABFB-F82A267C3134}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,9 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={D4B27D74-EED9-482B-A4F1-5CEE32155A2C}</author>
-    <author>tc={922D9E6B-3DB0-4618-8FE9-39316F3AF760}</author>
+    <author>tc={A6F94B31-257C-4300-BB2C-F707ED69A8C7}</author>
+    <author>tc={2657F045-E255-400A-AA3E-0CC46C6B6378}</author>
+    <author>tc={74CED45B-8FAB-4A3A-89E6-256D8AFFCB73}</author>
     <author>tc={E7E8705B-EDDF-4FF8-AF71-D79EA085E55F}</author>
   </authors>
   <commentList>
@@ -52,7 +54,7 @@
     About You Acq impact</t>
       </text>
     </comment>
-    <comment ref="N40" authorId="1" shapeId="0" xr:uid="{922D9E6B-3DB0-4618-8FE9-39316F3AF760}">
+    <comment ref="N40" authorId="1" shapeId="0" xr:uid="{A6F94B31-257C-4300-BB2C-F707ED69A8C7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -60,7 +62,23 @@
     AboutYou acq impact</t>
       </text>
     </comment>
-    <comment ref="Y40" authorId="2" shapeId="0" xr:uid="{E7E8705B-EDDF-4FF8-AF71-D79EA085E55F}">
+    <comment ref="O40" authorId="2" shapeId="0" xr:uid="{2657F045-E255-400A-AA3E-0CC46C6B6378}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    AboutYou acq impact</t>
+      </text>
+    </comment>
+    <comment ref="P40" authorId="3" shapeId="0" xr:uid="{74CED45B-8FAB-4A3A-89E6-256D8AFFCB73}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    AboutYou acq impact</t>
+      </text>
+    </comment>
+    <comment ref="Y40" authorId="4" shapeId="0" xr:uid="{E7E8705B-EDDF-4FF8-AF71-D79EA085E55F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -308,13 +326,19 @@
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -370,6 +394,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -390,30 +420,33 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -762,7 +795,13 @@
   <threadedComment ref="M40" dT="2026-03-13T10:55:36.16" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{D4B27D74-EED9-482B-A4F1-5CEE32155A2C}">
     <text>About You Acq impact</text>
   </threadedComment>
-  <threadedComment ref="N40" dT="2026-03-13T10:55:51.13" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{922D9E6B-3DB0-4618-8FE9-39316F3AF760}">
+  <threadedComment ref="N40" dT="2026-03-13T10:55:51.13" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{A6F94B31-257C-4300-BB2C-F707ED69A8C7}">
+    <text>AboutYou acq impact</text>
+  </threadedComment>
+  <threadedComment ref="O40" dT="2026-03-13T10:55:51.13" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{2657F045-E255-400A-AA3E-0CC46C6B6378}">
+    <text>AboutYou acq impact</text>
+  </threadedComment>
+  <threadedComment ref="P40" dT="2026-03-13T10:55:51.13" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{74CED45B-8FAB-4A3A-89E6-256D8AFFCB73}">
     <text>AboutYou acq impact</text>
   </threadedComment>
   <threadedComment ref="Y40" dT="2026-03-13T10:56:50.44" personId="{48AB04CC-2CEE-4DAA-8F96-EBFABD3AF0FB}" id="{E7E8705B-EDDF-4FF8-AF71-D79EA085E55F}">
@@ -794,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>19.87</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -802,10 +841,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>260.39999999999998</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>70</v>
+        <v>249</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -817,7 +856,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>5174.1480000000001</v>
+        <v>6292.23</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -828,10 +867,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>1259.7</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>70</v>
+        <v>1397.8</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -839,11 +878,11 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <f>484.1+8.1+223.5</f>
-        <v>715.7</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>70</v>
+        <f>696.5+242.5</f>
+        <v>939</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -852,7 +891,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>4630.1480000000001</v>
+        <v>5833.4299999999994</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1009,7 +1048,9 @@
       <c r="O3" s="3">
         <v>4294.3</v>
       </c>
-      <c r="P3" s="3"/>
+      <c r="P3" s="3">
+        <v>4915</v>
+      </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -1113,7 +1154,9 @@
       <c r="O4" s="3">
         <v>62.3</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3">
+        <v>62.5</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
@@ -1217,7 +1260,9 @@
       <c r="O5" s="3">
         <v>69.5</v>
       </c>
-      <c r="P5" s="3"/>
+      <c r="P5" s="3">
+        <v>77.5</v>
+      </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -1293,23 +1338,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D6" s="3" t="e">
-        <f t="shared" ref="D6:K6" si="0">+D3/D4</f>
+        <f>+D3/D4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="0"/>
+        <f>+E3/E4</f>
         <v>64.057884231536931</v>
       </c>
       <c r="F6" s="3" t="e">
-        <f t="shared" si="0"/>
+        <f>+F3/F4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="0"/>
+        <f>+G3/G4</f>
         <v>66.353535353535349</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="0"/>
+        <f>+H3/H4</f>
         <v>77.668674698795186</v>
       </c>
       <c r="I6" s="3">
@@ -1317,30 +1362,33 @@
         <v>68.757455268389663</v>
       </c>
       <c r="J6" s="3">
+        <f>+J3/J4</f>
+        <v>90.239382239382238</v>
+      </c>
+      <c r="K6" s="3">
+        <f>+K3/K4</f>
+        <v>75.299618320610691</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" ref="L6:O6" si="0">+L3/L4</f>
+        <v>76.71266540642722</v>
+      </c>
+      <c r="M6" s="3">
         <f t="shared" si="0"/>
-        <v>90.239382239382238</v>
-      </c>
-      <c r="K6" s="3">
+        <v>68.560260586319231</v>
+      </c>
+      <c r="N6" s="3">
         <f t="shared" si="0"/>
-        <v>75.299618320610691</v>
-      </c>
-      <c r="L6" s="3">
-        <f t="shared" ref="L6:O6" si="1">+L3/L4</f>
-        <v>76.71266540642722</v>
-      </c>
-      <c r="M6" s="3">
-        <f t="shared" si="1"/>
-        <v>68.560260586319231</v>
-      </c>
-      <c r="N6" s="3">
-        <f t="shared" si="1"/>
         <v>86.238709677419379</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>68.929373996789735</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3">
+        <f t="shared" ref="P6" si="1">+P3/P4</f>
+        <v>78.64</v>
+      </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -1469,7 +1517,10 @@
         <f t="shared" si="5"/>
         <v>1.115569823434992</v>
       </c>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3">
+        <f t="shared" ref="P7" si="6">+P5/P4</f>
+        <v>1.24</v>
+      </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -1547,27 +1598,27 @@
         <v>43</v>
       </c>
       <c r="C8" s="3" t="e">
-        <f t="shared" ref="C8:H8" si="6">+C3/C5</f>
+        <f>+C3/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D8" s="3" t="e">
-        <f t="shared" si="6"/>
+        <f>+D3/D5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="6"/>
+        <f>+E3/E5</f>
         <v>58.886238532110092</v>
       </c>
       <c r="F8" s="3" t="e">
-        <f t="shared" si="6"/>
+        <f>+F3/F5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="6"/>
+        <f>+G3/G5</f>
         <v>59.501811594202898</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="6"/>
+        <f>+H3/H5</f>
         <v>61.00788643533123</v>
       </c>
       <c r="I8" s="3">
@@ -1598,7 +1649,10 @@
         <f t="shared" si="8"/>
         <v>61.788489208633095</v>
       </c>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3">
+        <f t="shared" ref="P8" si="9">+P3/P5</f>
+        <v>63.41935483870968</v>
+      </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -1676,11 +1730,11 @@
         <v>44</v>
       </c>
       <c r="C9" s="8" t="e">
-        <f t="shared" ref="C9:D9" si="9">+C13/C3</f>
+        <f>+C13/C3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D9" s="8" t="e">
-        <f t="shared" si="9"/>
+        <f>+D13/D3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E9" s="8">
@@ -1688,71 +1742,74 @@
         <v>0.70884616583055493</v>
       </c>
       <c r="F9" s="8" t="e">
-        <f t="shared" ref="F9:Y9" si="10">+F13/F3</f>
+        <f>+F13/F3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="8">
+        <f>+G13/G3</f>
+        <v>0.68241741513167908</v>
+      </c>
+      <c r="H9" s="8">
+        <f>+H13/H3</f>
+        <v>0.68336823599369156</v>
+      </c>
+      <c r="I9" s="8">
+        <f>+I13/I3</f>
+        <v>0.69061731964724593</v>
+      </c>
+      <c r="J9" s="8">
+        <f>+J13/J3</f>
+        <v>0.70584460037651886</v>
+      </c>
+      <c r="K9" s="8">
+        <f>+K13/K3</f>
+        <v>0.61319917885292852</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" ref="L9:O9" si="10">+L13/L3</f>
+        <v>0.69862743648505454</v>
+      </c>
+      <c r="M9" s="8">
         <f t="shared" si="10"/>
-        <v>0.68241741513167908</v>
-      </c>
-      <c r="H9" s="8">
+        <v>0.71755036107943737</v>
+      </c>
+      <c r="N9" s="8">
         <f t="shared" si="10"/>
-        <v>0.68336823599369156</v>
-      </c>
-      <c r="I9" s="8">
+        <v>0.76137128749906469</v>
+      </c>
+      <c r="O9" s="8">
         <f t="shared" si="10"/>
-        <v>0.69061731964724593</v>
-      </c>
-      <c r="J9" s="8">
-        <f t="shared" si="10"/>
-        <v>0.70584460037651886</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="10"/>
-        <v>0.61319917885292852</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" ref="L9:O9" si="11">+L13/L3</f>
-        <v>0.69862743648505454</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" si="11"/>
-        <v>0.71755036107943737</v>
-      </c>
-      <c r="N9" s="8">
-        <f t="shared" si="11"/>
-        <v>0.76137128749906469</v>
-      </c>
-      <c r="O9" s="8">
-        <f t="shared" si="11"/>
         <v>0.69769228977947506</v>
       </c>
-      <c r="P9" s="8"/>
+      <c r="P9" s="8">
+        <f t="shared" ref="P9" si="11">+P13/P3</f>
+        <v>0.69672431332655138</v>
+      </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="3"/>
       <c r="T9" s="8">
-        <f t="shared" si="10"/>
+        <f>+T13/T3</f>
         <v>0.73784592370979807</v>
       </c>
       <c r="U9" s="8">
-        <f t="shared" si="10"/>
+        <f>+U13/U3</f>
         <v>0.72240401320058323</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" si="10"/>
+        <f>+V13/V3</f>
         <v>0.69950705606307506</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" si="10"/>
+        <f>+W13/W3</f>
         <v>0.69326088442348444</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="10"/>
+        <f>+X13/X3</f>
         <v>0.69118473869327024</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="10"/>
+        <f>+Y13/Y3</f>
         <v>0.70307285794011454</v>
       </c>
       <c r="Z9" s="3"/>
@@ -1901,7 +1958,9 @@
       <c r="O11" s="3">
         <v>2707.2</v>
       </c>
-      <c r="P11" s="3"/>
+      <c r="P11" s="3">
+        <v>3098.7</v>
+      </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -1994,7 +2053,9 @@
       <c r="O12" s="3">
         <v>296.7</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="3">
+        <v>334.7</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -2094,7 +2155,9 @@
       <c r="O13" s="9">
         <v>2996.1</v>
       </c>
-      <c r="P13" s="9"/>
+      <c r="P13" s="9">
+        <v>3424.4</v>
+      </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="3"/>
@@ -2200,7 +2263,9 @@
       <c r="O14" s="3">
         <v>1824.5</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <v>2025.6</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
@@ -2300,7 +2365,7 @@
         <v>971.8</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" ref="J15:O15" si="13">+J13-J14</f>
+        <f t="shared" ref="J15:P15" si="13">+J13-J14</f>
         <v>1374.1999999999998</v>
       </c>
       <c r="K15" s="3">
@@ -2323,7 +2388,10 @@
         <f t="shared" si="13"/>
         <v>1171.5999999999999</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3">
+        <f t="shared" si="13"/>
+        <v>1398.8000000000002</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
@@ -2435,7 +2503,9 @@
       <c r="O16" s="3">
         <v>750.8</v>
       </c>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3">
+        <v>792.2</v>
+      </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -2535,7 +2605,9 @@
       <c r="O17" s="3">
         <v>274.2</v>
       </c>
-      <c r="P17" s="3"/>
+      <c r="P17" s="3">
+        <v>328.3</v>
+      </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -2635,7 +2707,9 @@
       <c r="O18" s="3">
         <v>134.4</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3">
+        <v>137.80000000000001</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
@@ -2735,7 +2809,9 @@
       <c r="O19" s="3">
         <v>7.8</v>
       </c>
-      <c r="P19" s="3"/>
+      <c r="P19" s="3">
+        <v>13.6</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
@@ -2835,7 +2911,9 @@
       <c r="O20" s="3">
         <v>99.7</v>
       </c>
-      <c r="P20" s="3"/>
+      <c r="P20" s="3">
+        <v>43.1</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -2952,7 +3030,10 @@
         <f t="shared" si="16"/>
         <v>-79.700000000000188</v>
       </c>
-      <c r="P21" s="3"/>
+      <c r="P21" s="3">
+        <f t="shared" si="16"/>
+        <v>111.00000000000023</v>
+      </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -3064,7 +3145,9 @@
       <c r="O22" s="3">
         <v>4.4000000000000004</v>
       </c>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <v>3.5</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -3164,7 +3247,9 @@
       <c r="O23" s="3">
         <v>17.7</v>
       </c>
-      <c r="P23" s="3"/>
+      <c r="P23" s="3">
+        <v>17.899999999999999</v>
+      </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -3264,7 +3349,9 @@
       <c r="O24" s="3">
         <v>-9.1999999999999993</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <v>1.7</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -3381,7 +3468,10 @@
         <f t="shared" si="18"/>
         <v>-102.20000000000019</v>
       </c>
-      <c r="P25" s="3"/>
+      <c r="P25" s="3">
+        <f t="shared" si="18"/>
+        <v>98.300000000000225</v>
+      </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
@@ -3493,7 +3583,9 @@
       <c r="O26" s="3">
         <v>-14.6</v>
       </c>
-      <c r="P26" s="3"/>
+      <c r="P26" s="3">
+        <v>24.8</v>
+      </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -3597,7 +3689,9 @@
       <c r="O27" s="15">
         <v>0</v>
       </c>
-      <c r="P27" s="15"/>
+      <c r="P27" s="15">
+        <v>0</v>
+      </c>
       <c r="Q27" s="15"/>
       <c r="R27" s="15"/>
       <c r="S27" s="3"/>
@@ -3709,7 +3803,7 @@
         <v>96.599999999999966</v>
       </c>
       <c r="M28" s="3">
-        <f t="shared" ref="M28:O28" si="29">M25-M26-M27</f>
+        <f t="shared" ref="M28:P28" si="29">M25-M26-M27</f>
         <v>12.499999999999908</v>
       </c>
       <c r="N28" s="3">
@@ -3720,7 +3814,10 @@
         <f t="shared" si="29"/>
         <v>-87.600000000000193</v>
       </c>
-      <c r="P28" s="3"/>
+      <c r="P28" s="3">
+        <f t="shared" si="29"/>
+        <v>73.500000000000227</v>
+      </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -3903,39 +4000,42 @@
         <v>3.8981088382863939E-2</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" ref="L30:O30" si="32">+L28/L31</f>
+        <f>+L28/L31</f>
         <v>0.37111025739531295</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="32"/>
+        <f>+M28/M31</f>
         <v>4.8021513638109518E-2</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="32"/>
+        <f>+N28/N31</f>
         <v>0.36827956989246924</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="32"/>
+        <f>+O28/O31</f>
         <v>-0.33640552995391781</v>
       </c>
-      <c r="P30" s="10"/>
+      <c r="P30" s="10">
+        <f>+P28/P31</f>
+        <v>0.29518072289156716</v>
+      </c>
       <c r="Q30" s="10"/>
       <c r="R30" s="10"/>
       <c r="S30" s="3"/>
       <c r="T30" s="10" t="e">
-        <f t="shared" ref="T30:W30" si="33">+T28/T31</f>
+        <f t="shared" ref="T30:W30" si="32">+T28/T31</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U30" s="10" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V30" s="10" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0.31998459761263059</v>
       </c>
       <c r="X30" s="10">
@@ -4023,7 +4123,9 @@
       <c r="O31" s="3">
         <v>260.39999999999998</v>
       </c>
-      <c r="P31" s="3"/>
+      <c r="P31" s="3">
+        <v>249</v>
+      </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
@@ -4184,7 +4286,9 @@
       <c r="O33" s="11">
         <v>16998</v>
       </c>
-      <c r="P33" s="11"/>
+      <c r="P33" s="11">
+        <v>17417</v>
+      </c>
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
       <c r="S33" s="11"/>
@@ -4329,39 +4433,45 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="8" t="e">
-        <f t="shared" ref="G35:L37" si="34">+G3/C3-1</f>
+        <f>+G3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H35" s="8" t="e">
-        <f t="shared" si="34"/>
+        <f>+H3/D3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" si="34"/>
+        <f>+I3/E3-1</f>
         <v>7.7649331629950469E-2</v>
       </c>
       <c r="J35" s="8" t="e">
-        <f t="shared" si="34"/>
+        <f>+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="34"/>
+        <f>+K3/G3-1</f>
         <v>0.20130917947937266</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" si="34"/>
+        <f>+L3/H3-1</f>
         <v>4.9173970371519271E-2</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" ref="M35:M37" si="35">+M3/I3-1</f>
+        <f>+M3/I3-1</f>
         <v>0.21717507589995666</v>
       </c>
       <c r="N35" s="8">
-        <f t="shared" ref="N35:N37" si="36">+N3/J3-1</f>
+        <f t="shared" ref="N35:N37" si="33">+N3/J3-1</f>
         <v>0.14384733869587563</v>
       </c>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
+      <c r="O35" s="8">
+        <f t="shared" ref="O35:O37" si="34">+O3/K3-1</f>
+        <v>8.8349342322021629E-2</v>
+      </c>
+      <c r="P35" s="8">
+        <f t="shared" ref="P35:P37" si="35">+P3/L3-1</f>
+        <v>0.21115793105147729</v>
+      </c>
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
       <c r="S35" s="3"/>
@@ -4425,39 +4535,45 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="8" t="e">
+        <f>+G4/C4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H36" s="8" t="e">
+        <f>+H4/D4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I36" s="8">
+        <f>+I4/E4-1</f>
+        <v>3.9920159680637557E-3</v>
+      </c>
+      <c r="J36" s="8" t="e">
+        <f>+J4/F4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K36" s="8">
+        <f>+K4/G4-1</f>
+        <v>5.8585858585858519E-2</v>
+      </c>
+      <c r="L36" s="8">
+        <f>+L4/H4-1</f>
+        <v>6.2248995983935851E-2</v>
+      </c>
+      <c r="M36" s="8">
+        <f>+M4/I4-1</f>
+        <v>0.22067594433399607</v>
+      </c>
+      <c r="N36" s="8">
+        <f t="shared" si="33"/>
+        <v>0.19691119691119696</v>
+      </c>
+      <c r="O36" s="8">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H36" s="8" t="e">
-        <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I36" s="8">
-        <f t="shared" si="34"/>
-        <v>3.9920159680637557E-3</v>
-      </c>
-      <c r="J36" s="8" t="e">
-        <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K36" s="8">
-        <f t="shared" si="34"/>
-        <v>5.8585858585858519E-2</v>
-      </c>
-      <c r="L36" s="8">
-        <f t="shared" si="34"/>
-        <v>6.2248995983935851E-2</v>
-      </c>
-      <c r="M36" s="8">
+        <v>0.18893129770992356</v>
+      </c>
+      <c r="P36" s="8">
         <f t="shared" si="35"/>
-        <v>0.22067594433399607</v>
-      </c>
-      <c r="N36" s="8">
-        <f t="shared" si="36"/>
-        <v>0.19691119691119696</v>
-      </c>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
+        <v>0.18147448015122869</v>
+      </c>
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
       <c r="S36" s="3"/>
@@ -4521,39 +4637,45 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="8" t="e">
+        <f>+G5/C5-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H37" s="8" t="e">
+        <f>+H5/D5-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I37" s="8">
+        <f>+I5/E5-1</f>
+        <v>6.2385321100917324E-2</v>
+      </c>
+      <c r="J37" s="8" t="e">
+        <f>+J5/F5-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K37" s="8">
+        <f>+K5/G5-1</f>
+        <v>5.9782608695652106E-2</v>
+      </c>
+      <c r="L37" s="8">
+        <f>+L5/H5-1</f>
+        <v>2.5236593059936974E-2</v>
+      </c>
+      <c r="M37" s="8">
+        <f>+M5/I5-1</f>
+        <v>0.18307426597582044</v>
+      </c>
+      <c r="N37" s="8">
+        <f t="shared" si="33"/>
+        <v>2.7395973154362419</v>
+      </c>
+      <c r="O37" s="8">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H37" s="8" t="e">
-        <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I37" s="8">
-        <f t="shared" si="34"/>
-        <v>6.2385321100917324E-2</v>
-      </c>
-      <c r="J37" s="8" t="e">
-        <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K37" s="8">
-        <f t="shared" si="34"/>
-        <v>5.9782608695652106E-2</v>
-      </c>
-      <c r="L37" s="8">
-        <f t="shared" si="34"/>
-        <v>2.5236593059936974E-2</v>
-      </c>
-      <c r="M37" s="8">
+        <v>0.18803418803418803</v>
+      </c>
+      <c r="P37" s="8">
         <f t="shared" si="35"/>
-        <v>0.18307426597582044</v>
-      </c>
-      <c r="N37" s="8">
-        <f t="shared" si="36"/>
-        <v>2.7395973154362419</v>
-      </c>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
+        <v>0.19230769230769229</v>
+      </c>
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
       <c r="S37" s="3"/>
@@ -4617,57 +4739,63 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="8" t="e">
-        <f t="shared" ref="G38:G40" si="37">+G11/C11-1</f>
+        <f t="shared" ref="G38:G40" si="36">+G11/C11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H38" s="8" t="e">
-        <f t="shared" ref="H38:H40" si="38">+H11/D11-1</f>
+        <f t="shared" ref="H38:H40" si="37">+H11/D11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I38" s="8">
-        <f t="shared" ref="I38:I40" si="39">+I11/E11-1</f>
+        <f t="shared" ref="I38:I40" si="38">+I11/E11-1</f>
         <v>4.2898691226369356E-2</v>
       </c>
       <c r="J38" s="8" t="e">
-        <f t="shared" ref="J38:L40" si="40">+J11/F11-1</f>
+        <f t="shared" ref="J38:L40" si="39">+J11/F11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K38" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L38" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M38" s="8">
-        <f t="shared" ref="M38:M40" si="41">+M11/I11-1</f>
+        <f t="shared" ref="M38:M40" si="40">+M11/I11-1</f>
         <v>0.28361608180339282</v>
       </c>
       <c r="N38" s="8" t="e">
-        <f t="shared" ref="N38:N40" si="42">+N11/J11-1</f>
+        <f t="shared" ref="N38:N40" si="41">+N11/J11-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
+      <c r="O38" s="8">
+        <f t="shared" ref="O38:O40" si="42">+O11/K11-1</f>
+        <v>0.24041237113402047</v>
+      </c>
+      <c r="P38" s="8">
+        <f t="shared" ref="P38:P40" si="43">+P11/L11-1</f>
+        <v>0.2028647956212879</v>
+      </c>
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="8" t="e">
-        <f t="shared" ref="U38:X38" si="43">+U11/T11-1</f>
+        <f t="shared" ref="U38:X38" si="44">+U11/T11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V38" s="8" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W38" s="8" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X38" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>3.8261411769765052E-2</v>
       </c>
       <c r="Y38" s="8">
@@ -4728,57 +4856,63 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="8" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H39" s="8" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="8" t="e">
+      <c r="I39" s="8">
         <f t="shared" si="38"/>
+        <v>0.11075069508804436</v>
+      </c>
+      <c r="J39" s="8" t="e">
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I39" s="8">
+      <c r="K39" s="8" t="e">
         <f t="shared" si="39"/>
-        <v>0.11075069508804436</v>
-      </c>
-      <c r="J39" s="8" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L39" s="8" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M39" s="8">
         <f t="shared" si="40"/>
+        <v>0.15602836879432647</v>
+      </c>
+      <c r="N39" s="8" t="e">
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K39" s="8" t="e">
-        <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L39" s="8" t="e">
-        <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M39" s="8">
-        <f t="shared" si="41"/>
-        <v>0.15602836879432647</v>
-      </c>
-      <c r="N39" s="8" t="e">
+      <c r="O39" s="8">
         <f t="shared" si="42"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
+        <v>0.23624999999999985</v>
+      </c>
+      <c r="P39" s="8">
+        <f t="shared" si="43"/>
+        <v>0.27553353658536595</v>
+      </c>
       <c r="Q39" s="8"/>
       <c r="R39" s="8"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="8" t="e">
-        <f t="shared" ref="U39:X39" si="44">+U12/T12-1</f>
+        <f t="shared" ref="U39:X39" si="45">+U12/T12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V39" s="8" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W39" s="8" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X39" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.11493445692883908</v>
       </c>
       <c r="Y39" s="8">
@@ -4839,19 +4973,19 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="12" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H40" s="12" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="12" t="e">
+      <c r="I40" s="12">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I40" s="12">
+        <v>4.9936260934546617E-2</v>
+      </c>
+      <c r="J40" s="12" t="e">
         <f t="shared" si="39"/>
-        <v>4.9936260934546617E-2</v>
-      </c>
-      <c r="J40" s="12" t="e">
-        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K40" s="12">
@@ -4863,33 +4997,39 @@
         <v>7.2601392251816055E-2</v>
       </c>
       <c r="M40" s="12">
+        <f t="shared" si="40"/>
+        <v>0.26464308143186099</v>
+      </c>
+      <c r="N40" s="12">
         <f t="shared" si="41"/>
-        <v>0.26464308143186099</v>
-      </c>
-      <c r="N40" s="12">
+        <v>0.23383039340486156</v>
+      </c>
+      <c r="O40" s="12">
         <f t="shared" si="42"/>
-        <v>0.23383039340486156</v>
-      </c>
-      <c r="O40" s="12"/>
-      <c r="P40" s="12"/>
+        <v>0.23831370117792927</v>
+      </c>
+      <c r="P40" s="12">
+        <f t="shared" si="43"/>
+        <v>0.20785862932524424</v>
+      </c>
       <c r="Q40" s="12"/>
       <c r="R40" s="12"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="12">
-        <f t="shared" ref="U40:X40" si="45">+U13/T13-1</f>
+        <f t="shared" ref="U40:X40" si="46">+U13/T13-1</f>
         <v>0.31196147997972634</v>
       </c>
       <c r="V40" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-8.8854548966588176E-4</v>
       </c>
       <c r="W40" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-1.949771866058303E-2</v>
       </c>
       <c r="X40" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>4.2334197631887616E-2</v>
       </c>
       <c r="Y40" s="12">
@@ -4946,27 +5086,27 @@
         <v>49</v>
       </c>
       <c r="C41" s="8" t="e">
-        <f t="shared" ref="C41:H41" si="46">+C15/C13</f>
+        <f t="shared" ref="C41:H41" si="47">+C15/C13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D41" s="8" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E41" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.36691722713086289</v>
       </c>
       <c r="F41" s="8" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G41" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.38226108682073712</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.41585956416464886</v>
       </c>
       <c r="I41" s="8">
@@ -4986,37 +5126,43 @@
         <v>0.40827484039363693</v>
       </c>
       <c r="M41" s="8">
-        <f t="shared" ref="M41:N41" si="47">+M15/M13</f>
+        <f t="shared" ref="M41:N41" si="48">+M15/M13</f>
         <v>0.39568297689200815</v>
       </c>
       <c r="N41" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.39912550050357398</v>
       </c>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
+      <c r="O41" s="8">
+        <f t="shared" ref="O41:P41" si="49">+O15/O13</f>
+        <v>0.39104168752711854</v>
+      </c>
+      <c r="P41" s="8">
+        <f t="shared" si="49"/>
+        <v>0.40848031771989257</v>
+      </c>
       <c r="Q41" s="8"/>
       <c r="R41" s="8"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="8">
-        <f t="shared" ref="U41:Y41" si="48">+U15/U13</f>
+        <f t="shared" ref="U41:Y41" si="50">+U15/U13</f>
         <v>0.41783851651535642</v>
       </c>
       <c r="V41" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.39203271208723217</v>
       </c>
       <c r="W41" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.38749494730407869</v>
       </c>
       <c r="X41" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.40690470560416175</v>
       </c>
       <c r="Y41" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.39880610071196576</v>
       </c>
       <c r="Z41" s="3"/>
@@ -5069,27 +5215,27 @@
         <v>50</v>
       </c>
       <c r="C42" s="8" t="e">
-        <f t="shared" ref="C42:H42" si="49">+C21/C13</f>
+        <f t="shared" ref="C42:H42" si="51">+C21/C13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D42" s="8" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E42" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-8.2640995208580707E-3</v>
       </c>
       <c r="F42" s="8" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G42" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>2.6768983670929098E-4</v>
       </c>
       <c r="H42" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>5.8565375302663411E-2</v>
       </c>
       <c r="I42" s="8">
@@ -5109,37 +5255,43 @@
         <v>5.1250396811399937E-2</v>
       </c>
       <c r="M42" s="8">
-        <f t="shared" ref="M42:N42" si="50">+M21/M13</f>
+        <f t="shared" ref="M42:N42" si="52">+M21/M13</f>
         <v>1.6255048665827953E-2</v>
       </c>
       <c r="N42" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>4.2079147117344812E-2</v>
       </c>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
+      <c r="O42" s="8">
+        <f t="shared" ref="O42:P42" si="53">+O21/O13</f>
+        <v>-2.6601248289443005E-2</v>
+      </c>
+      <c r="P42" s="8">
+        <f t="shared" si="53"/>
+        <v>3.2414437565705008E-2</v>
+      </c>
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="8">
-        <f t="shared" ref="U42:Y42" si="51">+U21/U13</f>
+        <f t="shared" ref="U42:Y42" si="54">+U21/U13</f>
         <v>0.41783851651535642</v>
       </c>
       <c r="V42" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0.39203271208723217</v>
       </c>
       <c r="W42" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.8820676124656186E-2</v>
       </c>
       <c r="X42" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>3.7067864743438109E-2</v>
       </c>
       <c r="Y42" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>3.1362130551348254E-2</v>
       </c>
       <c r="Z42" s="3"/>
@@ -5192,27 +5344,27 @@
         <v>51</v>
       </c>
       <c r="C43" s="8" t="e">
-        <f t="shared" ref="C43:H43" si="52">+C26/C25</f>
+        <f t="shared" ref="C43:H43" si="55">+C26/C25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D43" s="8" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E43" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.62499999999999922</v>
       </c>
       <c r="F43" s="8" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G43" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.27200000000000446</v>
       </c>
       <c r="H43" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.35337837837837854</v>
       </c>
       <c r="I43" s="8">
@@ -5232,37 +5384,43 @@
         <v>0.33608247422680421</v>
       </c>
       <c r="M43" s="8">
-        <f t="shared" ref="M43:N43" si="53">+M26/M25</f>
+        <f t="shared" ref="M43:N43" si="56">+M26/M25</f>
         <v>0.66666666666666829</v>
       </c>
       <c r="N43" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>0.40559440559440818</v>
       </c>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
+      <c r="O43" s="8">
+        <f t="shared" ref="O43:P43" si="57">+O26/O25</f>
+        <v>0.1428571428571426</v>
+      </c>
+      <c r="P43" s="8">
+        <f t="shared" si="57"/>
+        <v>0.2522889114954216</v>
+      </c>
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="8">
-        <f t="shared" ref="U43:Y43" si="54">+U26/U25</f>
+        <f t="shared" ref="U43:Y43" si="58">+U26/U25</f>
         <v>0</v>
       </c>
       <c r="V43" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="W43" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>0.45686274509803876</v>
       </c>
       <c r="X43" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>0.31774938842076711</v>
       </c>
       <c r="Y43" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>0.40652901785714202</v>
       </c>
       <c r="Z43" s="3"/>
